--- a/testData/RegistrationData.xlsx
+++ b/testData/RegistrationData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Email</t>
   </si>
@@ -36,6 +36,66 @@
   </si>
   <si>
     <t>Test@930</t>
+  </si>
+  <si>
+    <t>lonmf897@gmail.com</t>
+  </si>
+  <si>
+    <t>Test@270</t>
+  </si>
+  <si>
+    <t>irrpr605@gmail.com</t>
+  </si>
+  <si>
+    <t>Test@812</t>
+  </si>
+  <si>
+    <t>bvumw481@gmail.com</t>
+  </si>
+  <si>
+    <t>Test@235</t>
+  </si>
+  <si>
+    <t>guzcn605@gmail.com</t>
+  </si>
+  <si>
+    <t>Test@196</t>
+  </si>
+  <si>
+    <t>szyxk883@gmail.com</t>
+  </si>
+  <si>
+    <t>Test@375</t>
+  </si>
+  <si>
+    <t>zradh526@gmail.com</t>
+  </si>
+  <si>
+    <t>Test@618</t>
+  </si>
+  <si>
+    <t>zrybx400@gmail.com</t>
+  </si>
+  <si>
+    <t>Test@361</t>
+  </si>
+  <si>
+    <t>sicbn263@gmail.com</t>
+  </si>
+  <si>
+    <t>Test@019</t>
+  </si>
+  <si>
+    <t>whids200@gmail.com</t>
+  </si>
+  <si>
+    <t>Test@792</t>
+  </si>
+  <si>
+    <t>xeqwb919@gmail.com</t>
+  </si>
+  <si>
+    <t>Test@012</t>
   </si>
 </sst>
 </file>
@@ -80,7 +140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -115,6 +175,86 @@
         <v>7</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/testData/RegistrationData.xlsx
+++ b/testData/RegistrationData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Email</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>Test@012</t>
+  </si>
+  <si>
+    <t>hlgox960@gmail.com</t>
+  </si>
+  <si>
+    <t>Test@648</t>
   </si>
 </sst>
 </file>
@@ -140,7 +146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -255,6 +261,14 @@
         <v>27</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
